--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
+++ b/ci-build/StructureDefinition-senologie-pathologie-befund.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3399" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: Pathologie</t>
   </si>
   <si>
     <t>Report
@@ -1997,7 +2003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ98"/>
+  <dimension ref="A1:AL98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="50.00390625" customWidth="true" bestFit="true"/>
@@ -2035,6 +2041,8 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.0078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2146,6 +2154,12 @@
       <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
+      <c r="AK1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="AL1" t="s" s="1">
+        <v>74</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2156,14 +2170,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2175,16 +2189,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2237,24 +2251,30 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2262,31 +2282,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2336,27 +2356,33 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2364,10 +2390,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2376,16 +2402,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2436,27 +2462,33 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL4" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2464,10 +2496,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -2479,13 +2511,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2536,38 +2568,44 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2579,16 +2617,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2626,39 +2664,45 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2666,10 +2710,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2678,19 +2722,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2740,27 +2784,33 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2768,31 +2818,31 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2842,27 +2892,33 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2870,10 +2926,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2882,19 +2938,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2944,27 +3000,33 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2972,31 +3034,31 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3046,27 +3108,33 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3074,10 +3142,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -3086,19 +3154,19 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3124,13 +3192,13 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>20</v>
@@ -3148,27 +3216,33 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3176,10 +3250,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -3188,19 +3262,19 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3226,13 +3300,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3250,27 +3324,33 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3278,31 +3358,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3352,27 +3432,33 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3380,10 +3466,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3395,16 +3481,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3430,13 +3516,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3454,41 +3540,47 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -3497,16 +3589,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3556,38 +3648,44 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3599,16 +3697,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3658,38 +3756,44 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3701,16 +3805,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3748,55 +3852,61 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3805,16 +3915,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3864,62 +3974,68 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3956,74 +4072,80 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4060,74 +4182,80 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4176,27 +4304,33 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4204,10 +4338,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4219,13 +4353,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4276,38 +4410,44 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4319,16 +4459,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4366,39 +4506,45 @@
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4406,34 +4552,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4458,13 +4604,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4482,27 +4628,33 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4510,34 +4662,34 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4547,7 +4699,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -4562,13 +4714,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4586,27 +4738,33 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4614,34 +4772,34 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4654,7 +4812,7 @@
         <v>20</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>20</v>
@@ -4690,27 +4848,33 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4718,31 +4882,31 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4756,7 +4920,7 @@
         <v>20</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>20</v>
@@ -4792,27 +4956,33 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4820,10 +4990,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4832,19 +5002,19 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4894,27 +5064,33 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4922,10 +5098,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4934,19 +5110,19 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4996,41 +5172,47 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -5039,19 +5221,19 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5100,27 +5282,33 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5128,41 +5316,41 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>20</v>
@@ -5180,13 +5368,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5204,59 +5392,65 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5282,13 +5476,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5306,59 +5500,65 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5384,13 +5584,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5408,27 +5608,33 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5436,10 +5642,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5451,13 +5657,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5508,38 +5714,44 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5551,16 +5763,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5598,39 +5810,45 @@
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5638,10 +5856,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5650,22 +5868,22 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5702,74 +5920,80 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5779,7 +6003,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -5818,27 +6042,33 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5846,10 +6076,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5861,13 +6091,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5918,38 +6148,44 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5961,16 +6197,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6008,39 +6244,45 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6048,34 +6290,34 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6124,27 +6366,33 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6152,10 +6400,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6164,19 +6412,19 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6226,27 +6474,33 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6254,34 +6508,34 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6330,27 +6584,33 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6358,10 +6618,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6370,22 +6630,22 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6434,27 +6694,33 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6462,10 +6728,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6474,22 +6740,22 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6538,27 +6804,33 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6566,10 +6838,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6578,22 +6850,22 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6603,7 +6875,7 @@
         <v>20</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>20</v>
@@ -6642,62 +6914,68 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6746,62 +7024,68 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -6850,62 +7134,68 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -6954,62 +7244,68 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7058,62 +7354,68 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7162,38 +7464,44 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7202,22 +7510,22 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7266,27 +7574,33 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7294,13 +7608,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>20</v>
@@ -7309,19 +7623,19 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7370,41 +7684,47 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
@@ -7413,19 +7733,19 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7462,53 +7782,59 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>20</v>
@@ -7517,19 +7843,19 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -7578,27 +7904,33 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7606,10 +7938,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -7621,13 +7953,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7678,38 +8010,44 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -7721,16 +8059,16 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7768,39 +8106,45 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7808,31 +8152,31 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7882,27 +8226,33 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7910,10 +8260,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -7922,19 +8272,19 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7960,13 +8310,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -7984,27 +8334,33 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8012,10 +8368,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8024,19 +8380,19 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8086,27 +8442,33 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8114,10 +8476,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8126,19 +8488,19 @@
         <v>20</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8188,43 +8550,49 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>20</v>
@@ -8233,19 +8601,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -8294,27 +8662,33 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8322,10 +8696,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -8337,13 +8711,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8394,38 +8768,44 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -8437,16 +8817,16 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8484,39 +8864,45 @@
         <v>20</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8524,31 +8910,31 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8598,27 +8984,33 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8626,10 +9018,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -8638,19 +9030,19 @@
         <v>20</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8676,13 +9068,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -8700,27 +9092,33 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8728,10 +9126,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -8740,19 +9138,19 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8802,27 +9200,33 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8830,10 +9234,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -8842,19 +9246,19 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8904,43 +9308,49 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>20</v>
@@ -8949,19 +9359,19 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9010,27 +9420,33 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9038,10 +9454,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9053,13 +9469,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9110,38 +9526,44 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9153,16 +9575,16 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9200,39 +9622,45 @@
         <v>20</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9240,31 +9668,31 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9314,27 +9742,33 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9342,10 +9776,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -9354,19 +9788,19 @@
         <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9392,13 +9826,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -9416,27 +9850,33 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9444,10 +9884,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -9456,19 +9896,19 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9518,27 +9958,33 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9546,10 +9992,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -9558,19 +10004,19 @@
         <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9620,43 +10066,49 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>20</v>
@@ -9665,19 +10117,19 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -9726,27 +10178,33 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9754,10 +10212,10 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -9769,13 +10227,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9826,38 +10284,44 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -9869,16 +10333,16 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9916,39 +10380,45 @@
         <v>20</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9956,31 +10426,31 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10030,27 +10500,33 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10058,10 +10534,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -10070,19 +10546,19 @@
         <v>20</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10108,13 +10584,13 @@
         <v>20</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>20</v>
@@ -10132,27 +10608,33 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10160,10 +10642,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -10172,19 +10654,19 @@
         <v>20</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10234,27 +10716,33 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10262,10 +10750,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
@@ -10274,19 +10762,19 @@
         <v>20</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10336,43 +10824,49 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>20</v>
@@ -10381,19 +10875,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -10442,27 +10936,33 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10470,10 +10970,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -10485,13 +10985,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10542,38 +11042,44 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL83" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -10585,16 +11091,16 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10632,39 +11138,45 @@
         <v>20</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10672,31 +11184,31 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10746,27 +11258,33 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10774,10 +11292,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -10786,19 +11304,19 @@
         <v>20</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10824,13 +11342,13 @@
         <v>20</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
@@ -10848,27 +11366,33 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10876,10 +11400,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
@@ -10888,19 +11412,19 @@
         <v>20</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10950,27 +11474,33 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10978,10 +11508,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -10990,19 +11520,19 @@
         <v>20</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11052,27 +11582,33 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11080,13 +11616,13 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>20</v>
@@ -11095,16 +11631,16 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11154,60 +11690,66 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -11256,27 +11798,33 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11284,10 +11832,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -11299,13 +11847,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11356,38 +11904,44 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -11399,16 +11953,16 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11446,74 +12000,80 @@
         <v>20</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -11562,27 +12122,33 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11590,10 +12156,10 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>20</v>
@@ -11605,19 +12171,19 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -11666,27 +12232,33 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11694,31 +12266,31 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11768,38 +12340,44 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>20</v>
@@ -11811,19 +12389,19 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -11872,27 +12450,33 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11900,13 +12484,13 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>20</v>
@@ -11915,16 +12499,16 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11950,13 +12534,13 @@
         <v>20</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -11974,27 +12558,33 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12002,13 +12592,13 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>20</v>
@@ -12017,19 +12607,19 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -12078,23 +12668,29 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ98">
+  <autoFilter ref="A1:AL98">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
